--- a/pacjenci/JAN TRACZ.xlsx
+++ b/pacjenci/JAN TRACZ.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/JAN TRACZ.xlsx
+++ b/pacjenci/JAN TRACZ.xlsx
@@ -413,279 +413,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>07.02.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 96mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywne metabolicznie węzły chłonne: liczne przedziału III po stronie prawej i liczne nadobojczykowe prawe oraz nieliczne nadobojczykowe lewe wielkości do 38x24mm wg PET, SUV max do 7,0.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.   Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - podobojczykowe lewe i prawe oraz pachowe prawe wielkości do 18x16mm wg PET, SUV max do 5,7; - przytchawicze górne lewe wielkości do 18x22mm wg PET, SUV max do 6,3. Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, obejmująca węzły chłonne śródpiersia, przy łuku aorty, przytchawicze obustronnie - o orientacyjnych największych wymiarach: 155x101x147mm wg PET, SUV max 9,5. Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału przemieszczone na stronę prawą, o wyraźnie zwężonym świetle. Przełyk przemieszczony na stronę prawą. W otoczeniu powyższej masy widoczne są inne zlewające się lub pojedyncze węzły chłonne środpiersia, wnęk obu płuc, podostrogowe - wielkości do 46mm, SUV max do 9,4.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Znacznie zwiększona ilość płynu w worku osierdziowym - o szerokości płaszcza od 27mm do 38mm [od strony PK]. Obszar obwodowych zagęszczeń miąższowych wielkości 11mm oraz zmiany niedodmowo-włókniste w segm. 6 płuca prawego. Miąższ płucny obustronnie uciśnięty przez patologiczne masy śródpiersiowe, Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.  Brzuch i miednica: Zwiekszona aktywność metaboliczna w prawej połowie okrężnicy- czynnościowo?- do ew. kontroli w endoskopii.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax do 1,3; Prawy płat wątroby SUVmax do 2,0.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego powyżej poziomu przepony. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>9.5</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>29.03.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Wczesna ocena odpowiedzi.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 88mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Drobny węzeł chłonny przy gałęzi żuchwy po stronie prawej wielkości 9mm, SUV max 2,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.   Klatka piersiowa i śródpiersie: Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, obejmująca węzły chłonne śródpiersia, przy łuku aorty, przytchawicze obustronnie głównie nieaktywna metabolicznie z drobnymi obszarami miernego pobudzenia metabolicznego, SUV max do 3,6- o orientacyjnych największych wymiarach: 111x80mm. Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału przemieszczone na stronę prawą, o wyraźnie zwężonym świetle. Przełyk przemieszczony na stronę prawą. W otoczeniu powyższej masy widoczne są inne zlewające się lub pojedyncze węzły chłonne środpiersia, wnęk obu płuc - wielkości do 16mm. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Znacznie zwiększona ilość płynu w worku osierdziowym - o szerokości płaszcza do 26mm od strony PK oraz do 17mm od strony LK. Zwiększona ilośc płynu w zachyłkach przeponowo-sercowych obustronnie. Drobne rozsiane obszary o typie "mlecznej szyby: w miąższu obu płuc -wiecej  Obszar obwodowych zagęszczeń miąższowych wielkości 11mm oraz zmiany niedodmowo-włókniste w segm. 6 płuca prawego. Miąższ płucny obustronnie uciśnięty przez patologiczne masy śródpiersiowe, Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.  Brzuch i miednica: Zwiekszona aktywność metaboliczna w prawej połowie okrężnicy- czynnościowo?- do ew. kontroli w endoskopii.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax do 1,2; Prawy płat wątroby SUVmax do 2,2.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono częściową regresję metaboliczną i radiologiczną choroby chłoniakowej w przebiegu stosowanego leczenia. Masy miękkotkankowe w śródpiersiu do dalszej kontroli - dokładna ocena wielkości mas możliwa w badaniu TK KLP z kontrastem dozylnym. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>04.08.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 86mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Ok. 9mm polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.   Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu przednim i środkowym, częściowo rozfragmentowana, obejmująca węzły chłonne śródpiersia, przy łuku aorty, przytchawicze obustronnie głównie nieaktywna metabolicznie z obszarami zwiększonej aktywności metabolicznej, wielkości 12mm wg PET, SUV max 5,5 oraz wielkości 11mm wg PET, SUV max 4,9 - o orientacyjnych największych wymiarach: 87x46mm.  Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału nadal przemieszczone na stronę prawą, o zwężonym świetle. Przełyk przemieszczony na stronę prawą. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 5,5mm obwodowy guzek oraz niewielkie zmiany włókniste w segm. 6 płuca prawego. Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.  Brzuch i miednica: Zwiększona aktywność metaboliczna w prawej połowie okrężnicy- czynnościowo?- do ew. kontroli w endoskopii.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Inne: Pobudzenie metaboliczne w tkance brunatnej szyi.   Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono głównie nieaktywną metabolicznie masę miękkotkankową w śródpiersiu, z dwoma aktywnymi metabolicznie obszarami - w porównaniu do badania z 29.03.2022 - aktualnie widoczne są dwie aktywne metabolicznie zmiany w obrębie miękkotkankowej masy.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>5.5</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>10.01.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena remisji choroby 3 miesiące po zakończeniu IFRT.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 98mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, o łącznych największych wymiarach: ok. 49x74mm, częściowo rozfragmentowana z obecnością aktywnych metabolicznie obszarów wielkości do 28x30mm, SUV max do 7,4 Aktywne metabolicznie węzły chłonne: - przytchawicze lewe wielkości do 20mm wg PET, SUV max do 5,7; - przy łuku aorty wielkości do 20mm wg PET, SUV max do 6,6; Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału nadal przemieszczone na stronę prawą, o zwężonym świetle. Przełyk przemieszczony na stronę prawą. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 5,5mm obwodowy guzek oraz niewielkie zmiany włókniste w segm. 6 płuca prawego. Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Inne: Pobudzenie metaboliczne w tkance brunatnej szyi po stronie lewej i w KLP, niewykluczona obecność drobnych węzłów chłonnych wśród pobudzonej tkanki brunatnej, SUV max do 3,4.  Wartości referencyjne: MBPS SUVmax do 1,4; Prawy płat wątroby SUVmax do 2,3.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie obszarów w obrębie rozległej masy w śródpiersiu oraz aktywnych metabolicznie węzłów chłonnych śródpiersia i KLP -  w porównaniu do badania PET z 29.03.2022 - progresja metaboliczna. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>7.4</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>28.02.2023</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Po zakończeniu IFRT. Ocena aktualnego statusu choroby.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 64 min od podania 18F-FDG. Glikemia: 87mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, o łącznych największych wymiarach: ok. 39x78mm, częściowo rozfragmentowana z obecnością aktywnych metabolicznie obszarów wielkości do 23x36mm, SUV max do 7,6 Aktywne metabolicznie węzły chłonne: - przytchawicze lewe wielkości do 26x23mm wg PET, SUV max do 8,0 [Im fuz 101]; - przy łuku aorty wielkości do 31x19mm wg PET, SUV max do 8,4 [Im fuz 109]; Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału nadal przemieszczone na stronę prawą, o nieco zwężonym świetle. Przełyk przemieszczony na stronę prawą. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 5,5mm obwodowy guzek oraz niewielkie zmiany włókniste w segm. 6 płuca prawego. Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba miernie powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie obszarów w obrębie rozległej masy w śródpiersiu oraz aktywnych metabolicznie węzłów chłonnych śródpiersia i KLP - w porównaniu do badania PET z 10.01.2023 - nadal aktywna choroba chłoniakowa.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>8.4</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/JAN TRACZ.xlsx
+++ b/pacjenci/JAN TRACZ.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 96mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne: liczne przedziału III po stronie prawej i liczne nadobojczykowe prawe oraz nieliczne nadobojczykowe lewe wielkości do 38x24mm wg PET, SUV max do 7,0.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.   Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - podobojczykowe lewe i prawe oraz pachowe prawe wielkości do 18x16mm wg PET, SUV max do 5,7; - przytchawicze górne lewe wielkości do 18x22mm wg PET, SUV max do 6,3. Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, obejmująca węzły chłonne śródpiersia, przy łuku aorty, przytchawicze obustronnie - o orientacyjnych największych wymiarach: 155x101x147mm wg PET, SUV max 9,5. Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału przemieszczone na stronę prawą, o wyraźnie zwężonym świetle. Przełyk przemieszczony na stronę prawą. W otoczeniu powyższej masy widoczne są inne zlewające się lub pojedyncze węzły chłonne środpiersia, wnęk obu płuc, podostrogowe - wielkości do 46mm, SUV max do 9,4.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Znacznie zwiększona ilość płynu w worku osierdziowym - o szerokości płaszcza od 27mm do 38mm [od strony PK]. Obszar obwodowych zagęszczeń miąższowych wielkości 11mm oraz zmiany niedodmowo-włókniste w segm. 6 płuca prawego. Miąższ płucny obustronnie uciśnięty przez patologiczne masy śródpiersiowe, Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.  Brzuch i miednica: Zwiekszona aktywność metaboliczna w prawej połowie okrężnicy- czynnościowo?- do ew. kontroli w endoskopii.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax do 1,3; Prawy płat wątroby SUVmax do 2,0.</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: liczne przedziału III po stronie prawej i liczne nadobojczykowe prawe oraz nieliczne nadobojczykowe lewe wielkości do 38x24mm wg PET, SUV max do 7,0.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - podobojczykowe lewe i prawe oraz pachowe prawe wielkości do 18x16mm wg PET, SUV max do 5,7; - przytchawicze górne lewe wielkości do 18x22mm wg PET, SUV max do 6,3. Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, obejmująca węzły chłonne śródpiersia, przy łuku aorty, przytchawicze obustronnie - o orientacyjnych największych wymiarach: 155x101x147mm wg PET, SUV max 9,5. Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału przemieszczone na stronę prawą, o wyraźnie zwężonym świetle. Przełyk przemieszczony na stronę prawą. W otoczeniu powyższej masy widoczne są inne zlewające się lub pojedyncze węzły chłonne środpiersia, wnęk obu płuc, podostrogowe - wielkości do 46mm, SUV max do 9,4.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Znacznie zwiększona ilość płynu w worku osierdziowym - o szerokości płaszcza od 27mm do 38mm [od strony PK]. Obszar obwodowych zagęszczeń miąższowych wielkości 11mm oraz zmiany niedodmowo-włókniste w segm. 6 płuca prawego. Miąższ płucny obustronnie uciśnięty przez patologiczne masy śródpiersiowe, Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Zwiekszona aktywność metaboliczna w prawej połowie okrężnicy- czynnościowo?- do ew. kontroli w endoskopii.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego powyżej poziomu przepony. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 88mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Drobny węzeł chłonny przy gałęzi żuchwy po stronie prawej wielkości 9mm, SUV max 2,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.   Klatka piersiowa i śródpiersie: Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, obejmująca węzły chłonne śródpiersia, przy łuku aorty, przytchawicze obustronnie głównie nieaktywna metabolicznie z drobnymi obszarami miernego pobudzenia metabolicznego, SUV max do 3,6- o orientacyjnych największych wymiarach: 111x80mm. Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału przemieszczone na stronę prawą, o wyraźnie zwężonym świetle. Przełyk przemieszczony na stronę prawą. W otoczeniu powyższej masy widoczne są inne zlewające się lub pojedyncze węzły chłonne środpiersia, wnęk obu płuc - wielkości do 16mm. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Znacznie zwiększona ilość płynu w worku osierdziowym - o szerokości płaszcza do 26mm od strony PK oraz do 17mm od strony LK. Zwiększona ilośc płynu w zachyłkach przeponowo-sercowych obustronnie. Drobne rozsiane obszary o typie "mlecznej szyby: w miąższu obu płuc -wiecej  Obszar obwodowych zagęszczeń miąższowych wielkości 11mm oraz zmiany niedodmowo-włókniste w segm. 6 płuca prawego. Miąższ płucny obustronnie uciśnięty przez patologiczne masy śródpiersiowe, Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.  Brzuch i miednica: Zwiekszona aktywność metaboliczna w prawej połowie okrężnicy- czynnościowo?- do ew. kontroli w endoskopii.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax do 1,2; Prawy płat wątroby SUVmax do 2,2.</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Drobny węzeł chłonny przy gałęzi żuchwy po stronie prawej wielkości 9mm, SUV max 2,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, obejmująca węzły chłonne śródpiersia, przy łuku aorty, przytchawicze obustronnie głównie nieaktywna metabolicznie z drobnymi obszarami miernego pobudzenia metabolicznego, SUV max do 3,6- o orientacyjnych największych wymiarach: 111x80mm. Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału przemieszczone na stronę prawą, o wyraźnie zwężonym świetle. Przełyk przemieszczony na stronę prawą. W otoczeniu powyższej masy widoczne są inne zlewające się lub pojedyncze węzły chłonne środpiersia, wnęk obu płuc - wielkości do 16mm. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Znacznie zwiększona ilość płynu w worku osierdziowym - o szerokości płaszcza do 26mm od strony PK oraz do 17mm od strony LK. Zwiększona ilośc płynu w zachyłkach przeponowo-sercowych obustronnie. Drobne rozsiane obszary o typie "mlecznej szyby: w miąższu obu płuc -wiecej  Obszar obwodowych zagęszczeń miąższowych wielkości 11mm oraz zmiany niedodmowo-włókniste w segm. 6 płuca prawego. Miąższ płucny obustronnie uciśnięty przez patologiczne masy śródpiersiowe, Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Zwiekszona aktywność metaboliczna w prawej połowie okrężnicy- czynnościowo?- do ew. kontroli w endoskopii.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono częściową regresję metaboliczną i radiologiczną choroby chłoniakowej w przebiegu stosowanego leczenia. Masy miękkotkankowe w śródpiersiu do dalszej kontroli - dokładna ocena wielkości mas możliwa w badaniu TK KLP z kontrastem dozylnym. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>3.6</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 86mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Ok. 9mm polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.   Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu przednim i środkowym, częściowo rozfragmentowana, obejmująca węzły chłonne śródpiersia, przy łuku aorty, przytchawicze obustronnie głównie nieaktywna metabolicznie z obszarami zwiększonej aktywności metabolicznej, wielkości 12mm wg PET, SUV max 5,5 oraz wielkości 11mm wg PET, SUV max 4,9 - o orientacyjnych największych wymiarach: 87x46mm.  Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału nadal przemieszczone na stronę prawą, o zwężonym świetle. Przełyk przemieszczony na stronę prawą. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 5,5mm obwodowy guzek oraz niewielkie zmiany włókniste w segm. 6 płuca prawego. Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.  Brzuch i miednica: Zwiększona aktywność metaboliczna w prawej połowie okrężnicy- czynnościowo?- do ew. kontroli w endoskopii.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Inne: Pobudzenie metaboliczne w tkance brunatnej szyi.   Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Ok. 9mm polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Masa miękkotkankowa w śródpiersiu przednim i środkowym, częściowo rozfragmentowana, obejmująca węzły chłonne śródpiersia, przy łuku aorty, przytchawicze obustronnie głównie nieaktywna metabolicznie z obszarami zwiększonej aktywności metabolicznej, wielkości 12mm wg PET, SUV max 5,5 oraz wielkości 11mm wg PET, SUV max 4,9 - o orientacyjnych największych wymiarach: 87x46mm.  Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału nadal przemieszczone na stronę prawą, o zwężonym świetle. Przełyk przemieszczony na stronę prawą. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 5,5mm obwodowy guzek oraz niewielkie zmiany włókniste w segm. 6 płuca prawego. Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Zwiększona aktywność metaboliczna w prawej połowie okrężnicy- czynnościowo?- do ew. kontroli w endoskopii.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Inne: Pobudzenie metaboliczne w tkance brunatnej szyi.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono głównie nieaktywną metabolicznie masę miękkotkankową w śródpiersiu, z dwoma aktywnymi metabolicznie obszarami - w porównaniu do badania z 29.03.2022 - aktualnie widoczne są dwie aktywne metabolicznie zmiany w obrębie miękkotkankowej masy.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 98mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, o łącznych największych wymiarach: ok. 49x74mm, częściowo rozfragmentowana z obecnością aktywnych metabolicznie obszarów wielkości do 28x30mm, SUV max do 7,4 Aktywne metabolicznie węzły chłonne: - przytchawicze lewe wielkości do 20mm wg PET, SUV max do 5,7; - przy łuku aorty wielkości do 20mm wg PET, SUV max do 6,6; Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału nadal przemieszczone na stronę prawą, o zwężonym świetle. Przełyk przemieszczony na stronę prawą. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 5,5mm obwodowy guzek oraz niewielkie zmiany włókniste w segm. 6 płuca prawego. Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Inne: Pobudzenie metaboliczne w tkance brunatnej szyi po stronie lewej i w KLP, niewykluczona obecność drobnych węzłów chłonnych wśród pobudzonej tkanki brunatnej, SUV max do 3,4.  Wartości referencyjne: MBPS SUVmax do 1,4; Prawy płat wątroby SUVmax do 2,3.</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, o łącznych największych wymiarach: ok. 49x74mm, częściowo rozfragmentowana z obecnością aktywnych metabolicznie obszarów wielkości do 28x30mm, SUV max do 7,4 Aktywne metabolicznie węzły chłonne: - przytchawicze lewe wielkości do 20mm wg PET, SUV max do 5,7; - przy łuku aorty wielkości do 20mm wg PET, SUV max do 6,6; Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału nadal przemieszczone na stronę prawą, o zwężonym świetle. Przełyk przemieszczony na stronę prawą. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 5,5mm obwodowy guzek oraz niewielkie zmiany włókniste w segm. 6 płuca prawego. Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Inne: Pobudzenie metaboliczne w tkance brunatnej szyi po stronie lewej i w KLP, niewykluczona obecność drobnych węzłów chłonnych wśród pobudzonej tkanki brunatnej, SUV max do 3,4.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie obszarów w obrębie rozległej masy w śródpiersiu oraz aktywnych metabolicznie węzłów chłonnych śródpiersia i KLP -  w porównaniu do badania PET z 29.03.2022 - progresja metaboliczna. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>7.4</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 64 min od podania 18F-FDG. Glikemia: 87mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, o łącznych największych wymiarach: ok. 39x78mm, częściowo rozfragmentowana z obecnością aktywnych metabolicznie obszarów wielkości do 23x36mm, SUV max do 7,6 Aktywne metabolicznie węzły chłonne: - przytchawicze lewe wielkości do 26x23mm wg PET, SUV max do 8,0 [Im fuz 101]; - przy łuku aorty wielkości do 31x19mm wg PET, SUV max do 8,4 [Im fuz 109]; Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału nadal przemieszczone na stronę prawą, o nieco zwężonym świetle. Przełyk przemieszczony na stronę prawą. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 5,5mm obwodowy guzek oraz niewielkie zmiany włókniste w segm. 6 płuca prawego. Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba miernie powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 2,6.</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Rozległa masa miękkotkankowa w śródpiersiu przednim i środkowym, o łącznych największych wymiarach: ok. 39x78mm, częściowo rozfragmentowana z obecnością aktywnych metabolicznie obszarów wielkości do 23x36mm, SUV max do 7,6 Aktywne metabolicznie węzły chłonne: - przytchawicze lewe wielkości do 26x23mm wg PET, SUV max do 8,0 [Im fuz 101]; - przy łuku aorty wielkości do 31x19mm wg PET, SUV max do 8,4 [Im fuz 109]; Struktury śródpiersia uciśnięte/nacieczone. Tchawica i oskrzela główne na poziomie podziału nadal przemieszczone na stronę prawą, o nieco zwężonym świetle. Przełyk przemieszczony na stronę prawą. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 5,5mm obwodowy guzek oraz niewielkie zmiany włókniste w segm. 6 płuca prawego. Niewielkie zmiany włókniste obustronnie przyśródpiersiowo i obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba miernie powiększona.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowe kręgosłupa. Poziome ułożenie kości krzyżowej.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie obszarów w obrębie rozległej masy w śródpiersiu oraz aktywnych metabolicznie węzłów chłonnych śródpiersia i KLP - w porównaniu do badania PET z 10.01.2023 - nadal aktywna choroba chłoniakowa.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>8.4</v>
       </c>
     </row>
